--- a/tools/AUTHORIZED STAFF.xlsx
+++ b/tools/AUTHORIZED STAFF.xlsx
@@ -496,7 +496,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9A5F-RJHB</t>
+          <t>4PUP-JZY7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
